--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/139.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/139.xlsx
@@ -426,13 +426,13 @@
         <v>-18.00164051537839</v>
       </c>
       <c r="E2">
-        <v>-13.76306254961756</v>
+        <v>-12.58459058775746</v>
       </c>
       <c r="F2">
-        <v>-2.130047884206373</v>
+        <v>-2.475246678888794</v>
       </c>
       <c r="G2">
-        <v>-7.756460374631458</v>
+        <v>-9.558876961851038</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.61192815317835</v>
       </c>
       <c r="E3">
-        <v>-14.76253299090247</v>
+        <v>-14.43511526319989</v>
       </c>
       <c r="F3">
-        <v>-2.233385487041755</v>
+        <v>-2.916069636745449</v>
       </c>
       <c r="G3">
-        <v>-7.616384571773816</v>
+        <v>-9.202327896725992</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.13311590540321</v>
       </c>
       <c r="E4">
-        <v>-15.95517907640658</v>
+        <v>-13.97284410802289</v>
       </c>
       <c r="F4">
-        <v>-1.963472112314537</v>
+        <v>-2.500102151378659</v>
       </c>
       <c r="G4">
-        <v>-6.709447379108317</v>
+        <v>-8.789814059259566</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.59348952347908</v>
       </c>
       <c r="E5">
-        <v>-14.83359833350484</v>
+        <v>-15.26357241205913</v>
       </c>
       <c r="F5">
-        <v>-2.203182631528409</v>
+        <v>-2.650407720548228</v>
       </c>
       <c r="G5">
-        <v>-7.188582635007036</v>
+        <v>-8.905656668769744</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.99088562437205</v>
       </c>
       <c r="E6">
-        <v>-15.8854677475325</v>
+        <v>-14.91521954901909</v>
       </c>
       <c r="F6">
-        <v>-2.163620865907774</v>
+        <v>-2.957895309972205</v>
       </c>
       <c r="G6">
-        <v>-6.34658841418542</v>
+        <v>-7.839455751300987</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.32830577515022</v>
       </c>
       <c r="E7">
-        <v>-17.50928342872893</v>
+        <v>-16.22208280594466</v>
       </c>
       <c r="F7">
-        <v>-2.379029417849228</v>
+        <v>-2.972146287652287</v>
       </c>
       <c r="G7">
-        <v>-6.542738237387238</v>
+        <v>-7.712019611312281</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.61679550957443</v>
       </c>
       <c r="E8">
-        <v>-17.28665006108983</v>
+        <v>-17.11063280488569</v>
       </c>
       <c r="F8">
-        <v>-1.7810125619438</v>
+        <v>-3.04624392817091</v>
       </c>
       <c r="G8">
-        <v>-5.61462679545256</v>
+        <v>-6.037942943013627</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.86002978933692</v>
       </c>
       <c r="E9">
-        <v>-16.81860510155306</v>
+        <v>-17.50960042190947</v>
       </c>
       <c r="F9">
-        <v>-2.214109410491984</v>
+        <v>-2.453114388720528</v>
       </c>
       <c r="G9">
-        <v>-5.69175919597204</v>
+        <v>-6.458428574138618</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.08180845546296</v>
       </c>
       <c r="E10">
-        <v>-18.94757205830511</v>
+        <v>-17.52174126072403</v>
       </c>
       <c r="F10">
-        <v>-2.242278787609905</v>
+        <v>-2.43016649000581</v>
       </c>
       <c r="G10">
-        <v>-5.63906524262346</v>
+        <v>-6.502283370897343</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.29652498998413</v>
       </c>
       <c r="E11">
-        <v>-18.97135107531939</v>
+        <v>-19.97779536657611</v>
       </c>
       <c r="F11">
-        <v>-2.135993116212933</v>
+        <v>-2.642641226738913</v>
       </c>
       <c r="G11">
-        <v>-5.426200474993862</v>
+        <v>-6.957874026920766</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.54582742564645</v>
       </c>
       <c r="E12">
-        <v>-17.96969790956279</v>
+        <v>-19.42592382468335</v>
       </c>
       <c r="F12">
-        <v>-1.751477238473812</v>
+        <v>-2.872177227299045</v>
       </c>
       <c r="G12">
-        <v>-4.249854396888013</v>
+        <v>-5.589556034083659</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.85613559179919</v>
       </c>
       <c r="E13">
-        <v>-19.51523891753663</v>
+        <v>-20.61442635647044</v>
       </c>
       <c r="F13">
-        <v>-1.667329400215811</v>
+        <v>-1.922414536456769</v>
       </c>
       <c r="G13">
-        <v>-4.44818918014575</v>
+        <v>-5.725867746663151</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.27657600849312</v>
       </c>
       <c r="E14">
-        <v>-21.68877058699817</v>
+        <v>-21.78688450484836</v>
       </c>
       <c r="F14">
-        <v>-1.898517997898703</v>
+        <v>-1.774430680159234</v>
       </c>
       <c r="G14">
-        <v>-4.977624864968155</v>
+        <v>-5.384845140117286</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.828297460785489</v>
       </c>
       <c r="E15">
-        <v>-21.57195407149631</v>
+        <v>-21.89860648709159</v>
       </c>
       <c r="F15">
-        <v>-1.762622568853718</v>
+        <v>-1.723005373526042</v>
       </c>
       <c r="G15">
-        <v>-3.644656877399387</v>
+        <v>-5.68208247136075</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.537417396762846</v>
       </c>
       <c r="E16">
-        <v>-22.01818990021215</v>
+        <v>-23.01094461454368</v>
       </c>
       <c r="F16">
-        <v>-1.219854085661352</v>
+        <v>-1.857298884037561</v>
       </c>
       <c r="G16">
-        <v>-3.629183387548833</v>
+        <v>-4.995716996340272</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.398456643176281</v>
       </c>
       <c r="E17">
-        <v>-23.42035489262914</v>
+        <v>-24.21217215829233</v>
       </c>
       <c r="F17">
-        <v>-1.072894095238149</v>
+        <v>-1.746952590673402</v>
       </c>
       <c r="G17">
-        <v>-3.895179100538195</v>
+        <v>-3.914367022483811</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.402847035412565</v>
       </c>
       <c r="E18">
-        <v>-24.37265222017615</v>
+        <v>-24.9125912330587</v>
       </c>
       <c r="F18">
-        <v>-1.019594472654034</v>
+        <v>-1.199244528730781</v>
       </c>
       <c r="G18">
-        <v>-3.960840460764099</v>
+        <v>-4.581580991559604</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.520787235825736</v>
       </c>
       <c r="E19">
-        <v>-24.70290024413352</v>
+        <v>-24.99166291770663</v>
       </c>
       <c r="F19">
-        <v>-0.3277770909360009</v>
+        <v>-0.8633278344187508</v>
       </c>
       <c r="G19">
-        <v>-3.370033882734685</v>
+        <v>-4.705891976559237</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.722545855753827</v>
       </c>
       <c r="E20">
-        <v>-25.15302603202195</v>
+        <v>-25.14684013652747</v>
       </c>
       <c r="F20">
-        <v>0.1486230284580433</v>
+        <v>-0.3270279980379981</v>
       </c>
       <c r="G20">
-        <v>-2.998872069599296</v>
+        <v>-4.562369895795213</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.971787428003921</v>
       </c>
       <c r="E21">
-        <v>-26.25751178554474</v>
+        <v>-25.7608604557015</v>
       </c>
       <c r="F21">
-        <v>-0.04126093524427329</v>
+        <v>-0.8749371906318797</v>
       </c>
       <c r="G21">
-        <v>-3.430345401369127</v>
+        <v>-4.158291328362851</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.2345714842677</v>
       </c>
       <c r="E22">
-        <v>-27.12898943747685</v>
+        <v>-26.9704973756824</v>
       </c>
       <c r="F22">
-        <v>0.7718413965958592</v>
+        <v>-0.01841914482589015</v>
       </c>
       <c r="G22">
-        <v>-3.511450456535732</v>
+        <v>-3.249874321841298</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.47904697077846</v>
       </c>
       <c r="E23">
-        <v>-26.26910920747838</v>
+        <v>-27.79203048778391</v>
       </c>
       <c r="F23">
-        <v>0.6179732809695088</v>
+        <v>-0.04257620300704576</v>
       </c>
       <c r="G23">
-        <v>-3.614593813357265</v>
+        <v>-4.505997926352504</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.67412501743767</v>
       </c>
       <c r="E24">
-        <v>-26.36413923452934</v>
+        <v>-28.25848142446999</v>
       </c>
       <c r="F24">
-        <v>0.5426197616599422</v>
+        <v>0.1803351557088028</v>
       </c>
       <c r="G24">
-        <v>-3.136210051295961</v>
+        <v>-4.76597175700593</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.79876790472644</v>
       </c>
       <c r="E25">
-        <v>-26.47124670175876</v>
+        <v>-28.79064504748137</v>
       </c>
       <c r="F25">
-        <v>1.168453620117106</v>
+        <v>0.2629539259054479</v>
       </c>
       <c r="G25">
-        <v>-3.575413506899991</v>
+        <v>-5.360178265304177</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.83473758278504</v>
       </c>
       <c r="E26">
-        <v>-27.9744510062349</v>
+        <v>-28.94142964651477</v>
       </c>
       <c r="F26">
-        <v>0.9885794696533248</v>
+        <v>0.2191121950483376</v>
       </c>
       <c r="G26">
-        <v>-3.479500381536226</v>
+        <v>-4.13830887548781</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.78412018609146</v>
       </c>
       <c r="E27">
-        <v>-28.35311747428229</v>
+        <v>-29.00956053796017</v>
       </c>
       <c r="F27">
-        <v>0.7718714870082526</v>
+        <v>0.2474660739054078</v>
       </c>
       <c r="G27">
-        <v>-3.901436031607417</v>
+        <v>-5.186821548140241</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.65401086696232</v>
       </c>
       <c r="E28">
-        <v>-27.30557728140596</v>
+        <v>-28.07425404488994</v>
       </c>
       <c r="F28">
-        <v>0.7571952842898751</v>
+        <v>-0.2977040993077212</v>
       </c>
       <c r="G28">
-        <v>-3.530125243922761</v>
+        <v>-5.48553207214868</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.47084539350904</v>
       </c>
       <c r="E29">
-        <v>-27.2031115000344</v>
+        <v>-27.73431961503016</v>
       </c>
       <c r="F29">
-        <v>0.8167141200039205</v>
+        <v>0.3162194988123805</v>
       </c>
       <c r="G29">
-        <v>-4.198143675564597</v>
+        <v>-5.448033522825356</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.25769375726454</v>
       </c>
       <c r="E30">
-        <v>-27.60584680743255</v>
+        <v>-28.27848822263588</v>
       </c>
       <c r="F30">
-        <v>0.8874234217164609</v>
+        <v>0.09090882563464123</v>
       </c>
       <c r="G30">
-        <v>-4.582696645406338</v>
+        <v>-4.314141880715121</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.04677427709215</v>
       </c>
       <c r="E31">
-        <v>-26.43099762477859</v>
+        <v>-27.57244025467797</v>
       </c>
       <c r="F31">
-        <v>0.7791137741595572</v>
+        <v>0.2377049024955968</v>
       </c>
       <c r="G31">
-        <v>-3.620367404777754</v>
+        <v>-4.532624644124862</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.8583479982378</v>
       </c>
       <c r="E32">
-        <v>-25.95475612728793</v>
+        <v>-26.44250447723208</v>
       </c>
       <c r="F32">
-        <v>0.5172123676585472</v>
+        <v>-3.390285355359991E-05</v>
       </c>
       <c r="G32">
-        <v>-3.633745319301949</v>
+        <v>-4.387424116772427</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.71370192264898</v>
       </c>
       <c r="E33">
-        <v>-25.94393307440959</v>
+        <v>-27.09027098471127</v>
       </c>
       <c r="F33">
-        <v>0.04227559253036896</v>
+        <v>0.03470231084273752</v>
       </c>
       <c r="G33">
-        <v>-4.400533877107941</v>
+        <v>-4.011693750792844</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.620652889097746</v>
       </c>
       <c r="E34">
-        <v>-25.01308259976291</v>
+        <v>-26.50838018862166</v>
       </c>
       <c r="F34">
-        <v>0.237190198073079</v>
+        <v>0.006837005260580443</v>
       </c>
       <c r="G34">
-        <v>-3.223866676084783</v>
+        <v>-4.629848745522178</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.588999854689451</v>
       </c>
       <c r="E35">
-        <v>-25.75570705228078</v>
+        <v>-26.24362295576321</v>
       </c>
       <c r="F35">
-        <v>0.1211536493547461</v>
+        <v>0.02614871519344907</v>
       </c>
       <c r="G35">
-        <v>-4.051738109635869</v>
+        <v>-4.827799505497359</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.615007884211224</v>
       </c>
       <c r="E36">
-        <v>-24.15611417855137</v>
+        <v>-26.3223142485945</v>
       </c>
       <c r="F36">
-        <v>0.02672360044075358</v>
+        <v>0.2640118414569614</v>
       </c>
       <c r="G36">
-        <v>-3.715356887936062</v>
+        <v>-5.019407260219297</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.695121491228976</v>
       </c>
       <c r="E37">
-        <v>-24.22095739786721</v>
+        <v>-24.01956710179809</v>
       </c>
       <c r="F37">
-        <v>0.1007943179588143</v>
+        <v>-0.323321334342912</v>
       </c>
       <c r="G37">
-        <v>-3.422939710997778</v>
+        <v>-3.881678695829047</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.812641926974026</v>
       </c>
       <c r="E38">
-        <v>-23.99910292775743</v>
+        <v>-24.92400298755803</v>
       </c>
       <c r="F38">
-        <v>0.5596548943393665</v>
+        <v>-0.5541686434010277</v>
       </c>
       <c r="G38">
-        <v>-2.53357489405473</v>
+        <v>-4.014888427238241</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.955572154591263</v>
       </c>
       <c r="E39">
-        <v>-23.24131261578788</v>
+        <v>-24.08897049443965</v>
       </c>
       <c r="F39">
-        <v>-0.1694896439526168</v>
+        <v>0.04768553193751011</v>
       </c>
       <c r="G39">
-        <v>-3.330002766073818</v>
+        <v>-3.617507093431824</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.10472290675152</v>
       </c>
       <c r="E40">
-        <v>-22.98487418968152</v>
+        <v>-24.56332361826911</v>
       </c>
       <c r="F40">
-        <v>0.1318610850490322</v>
+        <v>-0.4628664136700281</v>
       </c>
       <c r="G40">
-        <v>-3.59095320766133</v>
+        <v>-3.312327763439649</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.25060189794781</v>
       </c>
       <c r="E41">
-        <v>-22.069465811401</v>
+        <v>-24.13869766751787</v>
       </c>
       <c r="F41">
-        <v>0.5128571763910886</v>
+        <v>0.1781480578395809</v>
       </c>
       <c r="G41">
-        <v>-3.112036447768203</v>
+        <v>-3.835847503383377</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.37884951257205</v>
       </c>
       <c r="E42">
-        <v>-22.69703079633197</v>
+        <v>-23.3513726480703</v>
       </c>
       <c r="F42">
-        <v>-0.2033516519835853</v>
+        <v>-0.4058141999192797</v>
       </c>
       <c r="G42">
-        <v>-3.132227465012218</v>
+        <v>-2.778717480692223</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.4859569137094</v>
       </c>
       <c r="E43">
-        <v>-20.67800613153813</v>
+        <v>-22.58391857256838</v>
       </c>
       <c r="F43">
-        <v>0.3537984646268855</v>
+        <v>-0.8347308567036607</v>
       </c>
       <c r="G43">
-        <v>-2.960641889711792</v>
+        <v>-4.769811989831485</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.56587319960095</v>
       </c>
       <c r="E44">
-        <v>-20.30822000101979</v>
+        <v>-22.94868262541222</v>
       </c>
       <c r="F44">
-        <v>0.2482713883634088</v>
+        <v>-0.4005958889279067</v>
       </c>
       <c r="G44">
-        <v>-2.737236345085154</v>
+        <v>-4.280592812220147</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.62479814524548</v>
       </c>
       <c r="E45">
-        <v>-20.56515655926699</v>
+        <v>-21.91801099821446</v>
       </c>
       <c r="F45">
-        <v>0.1764622028925956</v>
+        <v>-0.07568040775747653</v>
       </c>
       <c r="G45">
-        <v>-3.291272693809884</v>
+        <v>-4.323702736232536</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.66555360476368</v>
       </c>
       <c r="E46">
-        <v>-19.57607443735568</v>
+        <v>-21.738262279428</v>
       </c>
       <c r="F46">
-        <v>0.2608444296260826</v>
+        <v>-0.4241186728899288</v>
       </c>
       <c r="G46">
-        <v>-2.915121888546813</v>
+        <v>-3.336402050601229</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.70175227457523</v>
       </c>
       <c r="E47">
-        <v>-19.59113614190519</v>
+        <v>-19.45489247291042</v>
       </c>
       <c r="F47">
-        <v>0.08618383903592763</v>
+        <v>-0.7173505335160775</v>
       </c>
       <c r="G47">
-        <v>-3.081754887720489</v>
+        <v>-4.022678140892146</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.74345264653634</v>
       </c>
       <c r="E48">
-        <v>-18.96070916140136</v>
+        <v>-21.40702704813695</v>
       </c>
       <c r="F48">
-        <v>0.3103526602486351</v>
+        <v>-0.2341824468924028</v>
       </c>
       <c r="G48">
-        <v>-2.744757904550379</v>
+        <v>-4.205658613938743</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.80553901422548</v>
       </c>
       <c r="E49">
-        <v>-18.13152745670089</v>
+        <v>-19.99057924869977</v>
       </c>
       <c r="F49">
-        <v>0.1500325267227844</v>
+        <v>-0.9717063731829763</v>
       </c>
       <c r="G49">
-        <v>-3.09755612157943</v>
+        <v>-4.720657009664387</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.8955780809352</v>
       </c>
       <c r="E50">
-        <v>-18.32999235856105</v>
+        <v>-20.28775129850512</v>
       </c>
       <c r="F50">
-        <v>-0.04444418413430658</v>
+        <v>-0.7385468534883191</v>
       </c>
       <c r="G50">
-        <v>-3.986325040325409</v>
+        <v>-4.830093713556074</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.01854405873559</v>
       </c>
       <c r="E51">
-        <v>-17.8339161449168</v>
+        <v>-19.0148697105331</v>
       </c>
       <c r="F51">
-        <v>0.211158032088043</v>
+        <v>-0.1160007685116071</v>
       </c>
       <c r="G51">
-        <v>-2.911602778638568</v>
+        <v>-4.218622710270529</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.17506104300411</v>
       </c>
       <c r="E52">
-        <v>-17.66156242418486</v>
+        <v>-20.13917206631345</v>
       </c>
       <c r="F52">
-        <v>0.0009962978444397607</v>
+        <v>-0.5307788907359025</v>
       </c>
       <c r="G52">
-        <v>-3.051638854949739</v>
+        <v>-4.23551642415743</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.36018499142721</v>
       </c>
       <c r="E53">
-        <v>-17.68000237034409</v>
+        <v>-18.28383815147488</v>
       </c>
       <c r="F53">
-        <v>0.1615935799054924</v>
+        <v>-0.4901758384758659</v>
       </c>
       <c r="G53">
-        <v>-2.599097211367986</v>
+        <v>-2.974092636237851</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.57032606130645</v>
       </c>
       <c r="E54">
-        <v>-16.91572728359556</v>
+        <v>-18.86099216375246</v>
       </c>
       <c r="F54">
-        <v>-0.0692157202106527</v>
+        <v>-0.3505808724124135</v>
       </c>
       <c r="G54">
-        <v>-3.305517971265368</v>
+        <v>-4.531744039011416</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.79658019089832</v>
       </c>
       <c r="E55">
-        <v>-16.9988745948504</v>
+        <v>-17.1996082621884</v>
       </c>
       <c r="F55">
-        <v>-0.03468538828336871</v>
+        <v>-0.3457759086649703</v>
       </c>
       <c r="G55">
-        <v>-3.618712132008119</v>
+        <v>-3.55842709773799</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.03831821459775</v>
       </c>
       <c r="E56">
-        <v>-15.76153699936459</v>
+        <v>-17.16284611019413</v>
       </c>
       <c r="F56">
-        <v>0.06466998602764046</v>
+        <v>-0.7686008406456134</v>
       </c>
       <c r="G56">
-        <v>-3.880682221621726</v>
+        <v>-3.607297370988712</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.28633942061563</v>
       </c>
       <c r="E57">
-        <v>-16.72613819079044</v>
+        <v>-17.11761571180552</v>
       </c>
       <c r="F57">
-        <v>-0.1006997938095889</v>
+        <v>-0.8101778720436452</v>
       </c>
       <c r="G57">
-        <v>-3.668049192179877</v>
+        <v>-4.834877451860321</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.54229443883544</v>
       </c>
       <c r="E58">
-        <v>-16.23476706164015</v>
+        <v>-15.36807147826013</v>
       </c>
       <c r="F58">
-        <v>-0.4070067304736056</v>
+        <v>-0.7478970532130735</v>
       </c>
       <c r="G58">
-        <v>-4.192975913977795</v>
+        <v>-5.183030973497775</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.79517142435068</v>
       </c>
       <c r="E59">
-        <v>-16.460208083164</v>
+        <v>-17.1815396508978</v>
       </c>
       <c r="F59">
-        <v>0.2292004017296869</v>
+        <v>-0.6876109119829977</v>
       </c>
       <c r="G59">
-        <v>-3.704680378571913</v>
+        <v>-4.548283524525615</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.04670861681871</v>
       </c>
       <c r="E60">
-        <v>-15.85032678923298</v>
+        <v>-15.29591024494791</v>
       </c>
       <c r="F60">
-        <v>-0.4351444334732182</v>
+        <v>-0.2208904031441195</v>
       </c>
       <c r="G60">
-        <v>-4.140000564258377</v>
+        <v>-5.295629248379467</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.28269384196286</v>
       </c>
       <c r="E61">
-        <v>-16.45212475706031</v>
+        <v>-17.22098265950461</v>
       </c>
       <c r="F61">
-        <v>0.2397866839214419</v>
+        <v>-0.4407269968251423</v>
       </c>
       <c r="G61">
-        <v>-4.343175365094529</v>
+        <v>-4.9959553556191</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.50236766693543</v>
       </c>
       <c r="E62">
-        <v>-15.91325446404357</v>
+        <v>-16.28869213012349</v>
       </c>
       <c r="F62">
-        <v>-0.03473210760787417</v>
+        <v>-0.4895779894927875</v>
       </c>
       <c r="G62">
-        <v>-3.881499926369926</v>
+        <v>-4.750792905708372</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.69109118298485</v>
       </c>
       <c r="E63">
-        <v>-16.10850414935828</v>
+        <v>-15.04208474834397</v>
       </c>
       <c r="F63">
-        <v>-0.1891632306871633</v>
+        <v>-0.3477468306767346</v>
       </c>
       <c r="G63">
-        <v>-3.923858356544901</v>
+        <v>-5.306146851557732</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.84788665445868</v>
       </c>
       <c r="E64">
-        <v>-14.55750633020519</v>
+        <v>-14.53273104890923</v>
       </c>
       <c r="F64">
-        <v>-0.4288903788131479</v>
+        <v>-0.4824592314028872</v>
       </c>
       <c r="G64">
-        <v>-4.443991408401955</v>
+        <v>-5.127582646260523</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.96094351413682</v>
       </c>
       <c r="E65">
-        <v>-15.59233056806798</v>
+        <v>-14.95179603357904</v>
       </c>
       <c r="F65">
-        <v>0.03066702817019781</v>
+        <v>-1.078726884124712</v>
       </c>
       <c r="G65">
-        <v>-4.99395578611338</v>
+        <v>-5.460001144949821</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.03127272550083</v>
       </c>
       <c r="E66">
-        <v>-14.4843624180333</v>
+        <v>-15.10124020430617</v>
       </c>
       <c r="F66">
-        <v>-0.4712790594928424</v>
+        <v>-0.6124141795590596</v>
       </c>
       <c r="G66">
-        <v>-3.903174068015535</v>
+        <v>-6.300009038447874</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.05360739159814</v>
       </c>
       <c r="E67">
-        <v>-15.55038784180894</v>
+        <v>-15.13792990071632</v>
       </c>
       <c r="F67">
-        <v>-0.0705808747097615</v>
+        <v>-1.527623574738277</v>
       </c>
       <c r="G67">
-        <v>-4.985388094257747</v>
+        <v>-5.132843103122425</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.03575340222715</v>
       </c>
       <c r="E68">
-        <v>-15.33975040181616</v>
+        <v>-15.23082248803566</v>
       </c>
       <c r="F68">
-        <v>-0.5786147279117509</v>
+        <v>-0.690082285064041</v>
       </c>
       <c r="G68">
-        <v>-4.757370959694904</v>
+        <v>-6.06046127377175</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.97946468086433</v>
       </c>
       <c r="E69">
-        <v>-15.8856443580188</v>
+        <v>-15.28726991654127</v>
       </c>
       <c r="F69">
-        <v>-0.3693952986878342</v>
+        <v>-1.04280685025663</v>
       </c>
       <c r="G69">
-        <v>-4.980412344312222</v>
+        <v>-5.379313218521165</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.8975256299921</v>
       </c>
       <c r="E70">
-        <v>-15.02597696629869</v>
+        <v>-14.53197026527594</v>
       </c>
       <c r="F70">
-        <v>-0.4900206352961529</v>
+        <v>-0.7354071565109603</v>
       </c>
       <c r="G70">
-        <v>-5.617424206433244</v>
+        <v>-5.196892227670704</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.79481743847625</v>
       </c>
       <c r="E71">
-        <v>-14.91058692010924</v>
+        <v>-15.0875008141669</v>
       </c>
       <c r="F71">
-        <v>-0.3122900307889186</v>
+        <v>-1.269404284490664</v>
       </c>
       <c r="G71">
-        <v>-3.912009914059849</v>
+        <v>-5.5974583062859</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.68464131264335</v>
       </c>
       <c r="E72">
-        <v>-14.95553655310938</v>
+        <v>-14.39046450948426</v>
       </c>
       <c r="F72">
-        <v>-0.3846503459183047</v>
+        <v>-1.030643988826055</v>
       </c>
       <c r="G72">
-        <v>-4.702667505203987</v>
+        <v>-5.999355224207883</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.57048323038011</v>
       </c>
       <c r="E73">
-        <v>-13.99881490645688</v>
+        <v>-14.73349641556529</v>
       </c>
       <c r="F73">
-        <v>-0.6139804647094292</v>
+        <v>-0.6811976948784257</v>
       </c>
       <c r="G73">
-        <v>-4.485009067633524</v>
+        <v>-5.815315376588719</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.4646495794927</v>
       </c>
       <c r="E74">
-        <v>-14.30100450546273</v>
+        <v>-15.54100937213906</v>
       </c>
       <c r="F74">
-        <v>-0.4604861036791226</v>
+        <v>-1.229927247136505</v>
       </c>
       <c r="G74">
-        <v>-4.732141292140119</v>
+        <v>-5.7422681892647</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.36794584280105</v>
       </c>
       <c r="E75">
-        <v>-14.92530446063417</v>
+        <v>-15.32391432821134</v>
       </c>
       <c r="F75">
-        <v>-0.8824669204068365</v>
+        <v>-1.496598775854818</v>
       </c>
       <c r="G75">
-        <v>-3.551107481550662</v>
+        <v>-3.905663598261067</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.2892878859949</v>
       </c>
       <c r="E76">
-        <v>-15.42045233710686</v>
+        <v>-15.57018633017048</v>
       </c>
       <c r="F76">
-        <v>-0.7821185624868467</v>
+        <v>-1.758373485882593</v>
       </c>
       <c r="G76">
-        <v>-4.217646099336444</v>
+        <v>-4.595339618820815</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.22435874940717</v>
       </c>
       <c r="E77">
-        <v>-15.95970302194024</v>
+        <v>-16.1465931442368</v>
       </c>
       <c r="F77">
-        <v>-0.7711466479046823</v>
+        <v>-0.8199635908951456</v>
       </c>
       <c r="G77">
-        <v>-3.527860830773899</v>
+        <v>-4.773754849568757</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.17950429657094</v>
       </c>
       <c r="E78">
-        <v>-15.43355774088506</v>
+        <v>-15.83975280242507</v>
       </c>
       <c r="F78">
-        <v>-0.6099372635073124</v>
+        <v>-1.640113414058984</v>
       </c>
       <c r="G78">
-        <v>-3.463159528754383</v>
+        <v>-3.943456786137387</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.14729558797046</v>
       </c>
       <c r="E79">
-        <v>-15.84646852937844</v>
+        <v>-16.04871470703501</v>
       </c>
       <c r="F79">
-        <v>-1.04822074892856</v>
+        <v>-1.246866565608045</v>
       </c>
       <c r="G79">
-        <v>-3.785563627187387</v>
+        <v>-4.361058932097672</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.13194096091778</v>
       </c>
       <c r="E80">
-        <v>-16.74071534862113</v>
+        <v>-17.77999107643346</v>
       </c>
       <c r="F80">
-        <v>-1.174668580334992</v>
+        <v>-1.827269444321956</v>
       </c>
       <c r="G80">
-        <v>-3.400384964238723</v>
+        <v>-3.97646292516392</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.12314465745237</v>
       </c>
       <c r="E81">
-        <v>-16.9179326504373</v>
+        <v>-17.37342468002481</v>
       </c>
       <c r="F81">
-        <v>-1.241661716116954</v>
+        <v>-2.009471642481433</v>
       </c>
       <c r="G81">
-        <v>-2.923236035663567</v>
+        <v>-4.464334710740776</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.12169806417844</v>
       </c>
       <c r="E82">
-        <v>-18.25097954407522</v>
+        <v>-17.62990839087125</v>
       </c>
       <c r="F82">
-        <v>-1.263113804594538</v>
+        <v>-2.136382707868131</v>
       </c>
       <c r="G82">
-        <v>-2.364502022818612</v>
+        <v>-3.687816459594865</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.11691033328298</v>
       </c>
       <c r="E83">
-        <v>-18.3945502840144</v>
+        <v>-19.69619673888314</v>
       </c>
       <c r="F83">
-        <v>-1.175243465582296</v>
+        <v>-2.153809807761627</v>
       </c>
       <c r="G83">
-        <v>-3.018205655548639</v>
+        <v>-3.423350218644647</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.10817812807271</v>
       </c>
       <c r="E84">
-        <v>-19.22145416628902</v>
+        <v>-18.2461838901011</v>
       </c>
       <c r="F84">
-        <v>-1.441656058383435</v>
+        <v>-1.909455862803686</v>
       </c>
       <c r="G84">
-        <v>-2.534147618433024</v>
+        <v>-2.963661107243607</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.08970032861982</v>
       </c>
       <c r="E85">
-        <v>-20.35826869575256</v>
+        <v>-19.76218566212291</v>
       </c>
       <c r="F85">
-        <v>-1.481826758928557</v>
+        <v>-1.97528814214963</v>
       </c>
       <c r="G85">
-        <v>-1.647745739747625</v>
+        <v>-3.369888218730957</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.06266276740586</v>
       </c>
       <c r="E86">
-        <v>-21.50964226915076</v>
+        <v>-20.79721368131605</v>
       </c>
       <c r="F86">
-        <v>-1.380553516753951</v>
+        <v>-2.115277450986027</v>
       </c>
       <c r="G86">
-        <v>-1.740762137764527</v>
+        <v>-3.427816144577124</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.0261091702503</v>
       </c>
       <c r="E87">
-        <v>-22.0443191952364</v>
+        <v>-22.99120046787024</v>
       </c>
       <c r="F87">
-        <v>-1.841190219318668</v>
+        <v>-2.290903310331643</v>
       </c>
       <c r="G87">
-        <v>-2.172748604092946</v>
+        <v>-3.099489480174365</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.98148144065929</v>
       </c>
       <c r="E88">
-        <v>-23.31839630034644</v>
+        <v>-23.74896360899574</v>
       </c>
       <c r="F88">
-        <v>-1.933265297536402</v>
+        <v>-2.191729270347951</v>
       </c>
       <c r="G88">
-        <v>-1.995157699184282</v>
+        <v>-2.689428756952539</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.9313582718516</v>
       </c>
       <c r="E89">
-        <v>-25.82540932420684</v>
+        <v>-25.92187487751823</v>
       </c>
       <c r="F89">
-        <v>-2.219444915721099</v>
+        <v>-2.652364389206753</v>
       </c>
       <c r="G89">
-        <v>-1.680930648233279</v>
+        <v>-3.639128266348804</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.87681661041515</v>
       </c>
       <c r="E90">
-        <v>-26.71750058982187</v>
+        <v>-26.50948966475354</v>
       </c>
       <c r="F90">
-        <v>-2.409995619613816</v>
+        <v>-2.69210986471358</v>
       </c>
       <c r="G90">
-        <v>-1.795773472990597</v>
+        <v>-1.913648757461887</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.82065495396045</v>
       </c>
       <c r="E91">
-        <v>-27.89276186361053</v>
+        <v>-28.88596489686882</v>
       </c>
       <c r="F91">
-        <v>-2.46561141209926</v>
+        <v>-2.844447328572658</v>
       </c>
       <c r="G91">
-        <v>-2.117684300138248</v>
+        <v>-3.817056846902473</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.75813163387656</v>
       </c>
       <c r="E92">
-        <v>-29.21426114852889</v>
+        <v>-30.08628221734193</v>
       </c>
       <c r="F92">
-        <v>-2.477814658030679</v>
+        <v>-2.7953437348115</v>
       </c>
       <c r="G92">
-        <v>-1.875061038656141</v>
+        <v>-3.605287869846374</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.68913113346633</v>
       </c>
       <c r="E93">
-        <v>-30.95223513098469</v>
+        <v>-30.21533240537552</v>
       </c>
       <c r="F93">
-        <v>-2.835587285828732</v>
+        <v>-3.018813349862541</v>
       </c>
       <c r="G93">
-        <v>-2.170666270948745</v>
+        <v>-3.547515539640552</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.60450648295166</v>
       </c>
       <c r="E94">
-        <v>-33.45097463283307</v>
+        <v>-33.96748105696293</v>
       </c>
       <c r="F94">
-        <v>-2.825943308656663</v>
+        <v>-3.588056644843307</v>
       </c>
       <c r="G94">
-        <v>-2.613120682272339</v>
+        <v>-4.206724609602388</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.50444634188365</v>
       </c>
       <c r="E95">
-        <v>-35.56608898759566</v>
+        <v>-34.13561650415672</v>
       </c>
       <c r="F95">
-        <v>-3.4890758169813</v>
+        <v>-3.4116777333349</v>
       </c>
       <c r="G95">
-        <v>-3.742188859531856</v>
+        <v>-3.719690392046969</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.38191105237729</v>
       </c>
       <c r="E96">
-        <v>-36.87632822189395</v>
+        <v>-37.60131653238894</v>
       </c>
       <c r="F96">
-        <v>-3.717544399754425</v>
+        <v>-3.978805989065597</v>
       </c>
       <c r="G96">
-        <v>-3.281493342286877</v>
+        <v>-4.007697922326944</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.24058327838319</v>
       </c>
       <c r="E97">
-        <v>-38.48339534197302</v>
+        <v>-39.03938553097575</v>
       </c>
       <c r="F97">
-        <v>-3.456607470155918</v>
+        <v>-3.638383651424142</v>
       </c>
       <c r="G97">
-        <v>-3.786507132666079</v>
+        <v>-4.675103903044016</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.08071668554636</v>
       </c>
       <c r="E98">
-        <v>-42.7974619550392</v>
+        <v>-41.85208187153891</v>
       </c>
       <c r="F98">
-        <v>-3.923931370948579</v>
+        <v>-4.062783578937689</v>
       </c>
       <c r="G98">
-        <v>-4.100396507972077</v>
+        <v>-5.03933674436571</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.91424794164113</v>
       </c>
       <c r="E99">
-        <v>-43.93110655269738</v>
+        <v>-42.77116963495067</v>
       </c>
       <c r="F99">
-        <v>-4.062975207353458</v>
+        <v>-4.635368493400033</v>
       </c>
       <c r="G99">
-        <v>-3.908080296504735</v>
+        <v>-5.608555254933537</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.75140724766673</v>
       </c>
       <c r="E100">
-        <v>-46.50767467307859</v>
+        <v>-45.62374598186238</v>
       </c>
       <c r="F100">
-        <v>-4.432841013521806</v>
+        <v>-4.524787811560389</v>
       </c>
       <c r="G100">
-        <v>-4.292666371801868</v>
+        <v>-5.255687516448161</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.60993988208495</v>
       </c>
       <c r="E101">
-        <v>-48.11047823487942</v>
+        <v>-48.73003800988334</v>
       </c>
       <c r="F101">
-        <v>-5.032820872909421</v>
+        <v>-4.945978359036299</v>
       </c>
       <c r="G101">
-        <v>-5.05078130029497</v>
+        <v>-6.146757264343933</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.50837471004334</v>
       </c>
       <c r="E102">
-        <v>-51.50402835098444</v>
+        <v>-52.1753338663555</v>
       </c>
       <c r="F102">
-        <v>-4.870095090098018</v>
+        <v>-4.921810214913735</v>
       </c>
       <c r="G102">
-        <v>-5.260994320947612</v>
+        <v>-6.493699126314014</v>
       </c>
     </row>
   </sheetData>
